--- a/out/D04_누락표시표_활동지.xlsx
+++ b/out/D04_누락표시표_활동지.xlsx
@@ -14,9 +14,11 @@
     <sheet name="5항목평가표" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="시간기록지" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="검증지표표" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="필수항목표" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="용어사전" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="표본목록" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="후보B_견적비교준비" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="후보C_발주입고_공동조회" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="필수항목표" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="용어사전" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="표본목록" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -593,6 +595,662 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:G7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="50" customWidth="1" min="5" max="5"/>
+    <col width="50" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>자재군</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>항목ID</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>항목명</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>구분</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>충족조건</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>모호조건</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>중요항목</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>배관</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>item_id</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>품목 ID</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>공통</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>P-NN 형식의 품목 ID가 원문에 있고 사전에 존재</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>별칭·표준명만 있음(표준명 후보로 제안), 후보가 2개 이상, 판독 불가 글자</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>배관</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>qty</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>수량</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>공통</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>양의 정수</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>판독 불가 글자(예: 2O)</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>배관</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>단위</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>공통</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>사전의 표준 단위와 같음(EA=개, M=m 동의어 허용)</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>품목이 확정되지 않아 비교 불가, 판독 불가</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>배관</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>need_date</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>희망일</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>공통</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>특정 날짜(YYYY-MM-DD, M월 D일, M/D)</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>'다음 주', 'ASAP', '빨리', '이번 달 안' 등 기간·정도 표현. 날짜로 단정하지 않음</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>배관</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>delivery_location</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>배송 위치</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>공통</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>현장명 + 세부 위치(동·층·창고·게이트 등)</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>현장명만 있음</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>배관</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>spec</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>규격</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>자재군추가</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>규격 토큰(50A, 100A, 12mm 등)이 있거나, 품목 ID가 확정되어 사전 규격을 적용할 수 있음</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>판독 불가. 품목 ID 없이 별칭만 있고 규격도 없으면 누락</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="44" customWidth="1" min="5" max="5"/>
+    <col width="50" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>품목ID</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>표준명</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>규격</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>표준단위</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>별칭</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>주의</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>P-01</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>볼밸브</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>50A</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>개</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>볼밸브; 볼발브; 밸브; ball valve</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>P-02(100A)와 별칭이 같음 → 규격 없으면 병합 금지</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>P-02</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>볼밸브</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>100A</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>개</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>볼밸브; 볼발브; 밸브; ball valve</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>P-01(50A)와 별칭이 같음 → 규격 없으면 병합 금지</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>P-03</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>PVC 파이프</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>50A</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>본</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>PVC 파이프; PVC관; PVC파이프; 피브이씨 파이프; pvc pipe</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>P-04(100A)와 별칭이 같음 → 규격 없으면 병합 금지</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>P-04</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>PVC 파이프</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>100A</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>본</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>PVC 파이프; PVC관; PVC파이프; 피브이씨 파이프; pvc pipe</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>P-03(50A)와 별칭이 같음 → 규격 없으면 병합 금지</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>P-05</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>강관</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>50A</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>본</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>강관; 백관; 스틸파이프; steel pipe</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>P-06(100A)와 별칭이 같음</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>P-06</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>강관</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>100A</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>본</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>강관; 백관; 스틸파이프; steel pipe</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>P-05(50A)와 별칭이 같음</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>P-07</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>PVC 엘보 90도</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>50A</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>개</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>엘보; 엘보우; 90도 엘보; elbow</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>P-08(45도)과 '엘보' 별칭 공유 → 각도 확인</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>P-08</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>PVC 엘보 45도</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>50A</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>개</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>엘보; 엘보우; 45도 엘보; 45엘보</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>P-07(90도)과 '엘보' 별칭 공유 → 각도 확인</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>P-09</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>배관 보온재</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>50A</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>보온재; 단열재; 인슐레이션</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>길이 단위(m). 개수로 요청 오면 불일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>P-10</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>테프론 테이프</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>12mm</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>롤</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>테프론; 테플론 테이프; 씰테이프; 테프론 테이프</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>롤 단위. 개수로 요청 오면 불일치</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:E60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -4223,278 +4881,479 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:N9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="50" customWidth="1" min="5" max="5"/>
-    <col width="50" customWidth="1" min="6" max="6"/>
-    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="9" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="30" customWidth="1" min="12" max="12"/>
+    <col width="18" customWidth="1" min="13" max="13"/>
+    <col width="34" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>자재군</t>
+          <t>업체</t>
         </is>
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>항목ID</t>
+          <t>품목ID</t>
         </is>
       </c>
       <c r="C1" s="4" t="inlineStr">
         <is>
-          <t>항목명</t>
+          <t>표기 품명</t>
         </is>
       </c>
       <c r="D1" s="4" t="inlineStr">
         <is>
-          <t>구분</t>
+          <t>단가(원)</t>
         </is>
       </c>
       <c r="E1" s="4" t="inlineStr">
         <is>
-          <t>충족조건</t>
+          <t>단가 단위</t>
         </is>
       </c>
       <c r="F1" s="4" t="inlineStr">
         <is>
-          <t>모호조건</t>
+          <t>포장 단위</t>
         </is>
       </c>
       <c r="G1" s="4" t="inlineStr">
         <is>
-          <t>중요항목</t>
+          <t>배송비 조건</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>납기</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>표준 단위(사전)</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>단위 일치?</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
+          <t>비교 가능?</t>
+        </is>
+      </c>
+      <c r="L1" s="4" t="inlineStr">
+        <is>
+          <t>확인 필요 사항</t>
+        </is>
+      </c>
+      <c r="M1" s="4" t="inlineStr">
+        <is>
+          <t>사람 확정</t>
+        </is>
+      </c>
+      <c r="N1" s="4" t="inlineStr">
+        <is>
+          <t>비고(교육용 함정 설명)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>배관</t>
+          <t>가나상사</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>item_id</t>
+          <t>P-03</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>품목 ID</t>
+          <t>PVC 파이프 50A</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>공통</t>
+          <t>8,500</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>P-NN 형식의 품목 ID가 원문에 있고 사전에 존재</t>
+          <t>본</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>별칭·표준명만 있음(표준명 후보로 제안), 후보가 2개 이상, 판독 불가 글자</t>
+          <t>10본/묶음</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
+          <t>50만원 이상 무료</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>발주 후 3일</t>
+        </is>
+      </c>
+      <c r="I2" s="2">
+        <f>IFERROR(VLOOKUP(B2,용어사전!$A:$D,4,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="J2" s="2">
+        <f>IF(OR(E2="",I2=""),"",IF(OR(E2=I2,AND(E2="EA",I2="개")),"예","아니오"))</f>
+        <v/>
+      </c>
+      <c r="K2" s="2" t="inlineStr"/>
+      <c r="L2" s="2" t="inlineStr"/>
+      <c r="M2" s="5" t="inlineStr"/>
+      <c r="N2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>배관</t>
+          <t>다라자재</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>qty</t>
+          <t>P-03</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>수량</t>
+          <t>PVC관 50A</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>공통</t>
+          <t>1,750</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>양의 정수</t>
+          <t>m</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>판독 불가 글자(예: 2O)</t>
+          <t>4m/본</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>별도 청구</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>발주 후 2일</t>
+        </is>
+      </c>
+      <c r="I3" s="2">
+        <f>IFERROR(VLOOKUP(B3,용어사전!$A:$D,4,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="J3" s="2">
+        <f>IF(OR(E3="",I3=""),"",IF(OR(E3=I3,AND(E3="EA",I3="개")),"예","아니오"))</f>
+        <v/>
+      </c>
+      <c r="K3" s="2" t="inlineStr"/>
+      <c r="L3" s="2" t="inlineStr"/>
+      <c r="M3" s="5" t="inlineStr"/>
+      <c r="N3" s="2" t="inlineStr">
+        <is>
+          <t>단가 단위가 m → 본 환산 필요</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>배관</t>
+          <t>마바건자재</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>unit</t>
+          <t>P-03</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>단위</t>
+          <t>PVC 파이프</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>공통</t>
+          <t>8,200</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>사전의 표준 단위와 같음(EA=개, M=m 동의어 허용)</t>
+          <t>본</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>품목이 확정되지 않아 비교 불가, 판독 불가</t>
+          <t>미기재</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>미기재</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>협의</t>
+        </is>
+      </c>
+      <c r="I4" s="2">
+        <f>IFERROR(VLOOKUP(B4,용어사전!$A:$D,4,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="J4" s="2">
+        <f>IF(OR(E4="",I4=""),"",IF(OR(E4=I4,AND(E4="EA",I4="개")),"예","아니오"))</f>
+        <v/>
+      </c>
+      <c r="K4" s="2" t="inlineStr"/>
+      <c r="L4" s="2" t="inlineStr"/>
+      <c r="M4" s="5" t="inlineStr"/>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>규격·배송비 미기재 → 비교 불가 표시</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>배관</t>
+          <t>가나상사</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>need_date</t>
+          <t>P-01</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>희망일</t>
+          <t>볼밸브 50A</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>공통</t>
+          <t>12,000</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>특정 날짜(YYYY-MM-DD, M월 D일, M/D)</t>
+          <t>개</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>'다음 주', 'ASAP', '빨리', '이번 달 안' 등 기간·정도 표현. 날짜로 단정하지 않음</t>
+          <t>1개</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
+          <t>50만원 이상 무료</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>발주 후 3일</t>
+        </is>
+      </c>
+      <c r="I5" s="2">
+        <f>IFERROR(VLOOKUP(B5,용어사전!$A:$D,4,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="J5" s="2">
+        <f>IF(OR(E5="",I5=""),"",IF(OR(E5=I5,AND(E5="EA",I5="개")),"예","아니오"))</f>
+        <v/>
+      </c>
+      <c r="K5" s="2" t="inlineStr"/>
+      <c r="L5" s="2" t="inlineStr"/>
+      <c r="M5" s="5" t="inlineStr"/>
+      <c r="N5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>배관</t>
+          <t>다라자재</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>delivery_location</t>
+          <t>P-01</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>배송 위치</t>
+          <t>볼밸브</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>공통</t>
+          <t>11,500</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>현장명 + 세부 위치(동·층·창고·게이트 등)</t>
+          <t>EA</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>현장명만 있음</t>
+          <t>1EA</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>현장 직납 시 3만원</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>발주 후 5일</t>
+        </is>
+      </c>
+      <c r="I6" s="2">
+        <f>IFERROR(VLOOKUP(B6,용어사전!$A:$D,4,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="J6" s="2">
+        <f>IF(OR(E6="",I6=""),"",IF(OR(E6=I6,AND(E6="EA",I6="개")),"예","아니오"))</f>
+        <v/>
+      </c>
+      <c r="K6" s="2" t="inlineStr"/>
+      <c r="L6" s="2" t="inlineStr"/>
+      <c r="M6" s="5" t="inlineStr"/>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>규격 미기재(50A/100A?) → 확인</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>배관</t>
+          <t>마바건자재</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>spec</t>
+          <t>P-01</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>규격</t>
+          <t>볼밸브 50A</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>자재군추가</t>
+          <t>10,900</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>규격 토큰(50A, 100A, 12mm 등)이 있거나, 품목 ID가 확정되어 사전 규격을 적용할 수 있음</t>
+          <t>개</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>판독 불가. 품목 ID 없이 별칭만 있고 규격도 없으면 누락</t>
+          <t>10개/박스</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
+          <t>박스 단위만 무료</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>발주 후 4일</t>
+        </is>
+      </c>
+      <c r="I7" s="2">
+        <f>IFERROR(VLOOKUP(B7,용어사전!$A:$D,4,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="J7" s="2">
+        <f>IF(OR(E7="",I7=""),"",IF(OR(E7=I7,AND(E7="EA",I7="개")),"예","아니오"))</f>
+        <v/>
+      </c>
+      <c r="K7" s="2" t="inlineStr"/>
+      <c r="L7" s="2" t="inlineStr"/>
+      <c r="M7" s="5" t="inlineStr"/>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>포장 단위 조건 확인</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="n"/>
+      <c r="B8" s="2" t="n"/>
+      <c r="C8" s="2" t="n"/>
+      <c r="D8" s="2" t="n"/>
+      <c r="E8" s="2" t="n"/>
+      <c r="F8" s="2" t="n"/>
+      <c r="G8" s="2" t="n"/>
+      <c r="H8" s="2" t="n"/>
+      <c r="I8" s="2" t="n"/>
+      <c r="J8" s="2" t="n"/>
+      <c r="K8" s="2" t="n"/>
+      <c r="L8" s="2" t="n"/>
+      <c r="M8" s="2" t="n"/>
+      <c r="N8" s="2" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>안내: 단가 단위가 표준 단위와 다르면(예: m ↔ 본) 환산 근거 없이는 '비교 불가'로 둔다. 배송비·규격 미기재도 비교 불가. 최저가는 사람이 조건을 확정한 뒤에만 본다.</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n"/>
+      <c r="C9" s="2" t="n"/>
+      <c r="D9" s="2" t="n"/>
+      <c r="E9" s="2" t="n"/>
+      <c r="F9" s="2" t="n"/>
+      <c r="G9" s="2" t="n"/>
+      <c r="H9" s="2" t="n"/>
+      <c r="I9" s="2" t="n"/>
+      <c r="J9" s="2" t="n"/>
+      <c r="K9" s="2" t="n"/>
+      <c r="L9" s="2" t="n"/>
+      <c r="M9" s="2" t="n"/>
+      <c r="N9" s="2" t="n"/>
     </row>
   </sheetData>
+  <dataValidations count="1">
+    <dataValidation sqref="K2 K3 K4 K5 K6 K7" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"예,아니오,확인 필요"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4505,368 +5364,477 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:Q8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
     <col width="8" customWidth="1" min="4" max="4"/>
-    <col width="44" customWidth="1" min="5" max="5"/>
-    <col width="50" customWidth="1" min="6" max="6"/>
+    <col width="9" customWidth="1" min="5" max="5"/>
+    <col width="6" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="8" customWidth="1" min="11" max="11"/>
+    <col width="11" customWidth="1" min="12" max="12"/>
+    <col width="8" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="30" customWidth="1" min="15" max="15"/>
+    <col width="18" customWidth="1" min="16" max="16"/>
+    <col width="40" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
+          <t>발주번호</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
           <t>품목ID</t>
         </is>
       </c>
-      <c r="B1" s="4" t="inlineStr">
-        <is>
-          <t>표준명</t>
-        </is>
-      </c>
       <c r="C1" s="4" t="inlineStr">
         <is>
-          <t>규격</t>
+          <t>품명</t>
         </is>
       </c>
       <c r="D1" s="4" t="inlineStr">
         <is>
-          <t>표준단위</t>
+          <t>현장</t>
         </is>
       </c>
       <c r="E1" s="4" t="inlineStr">
         <is>
-          <t>별칭</t>
+          <t>발주수량</t>
         </is>
       </c>
       <c r="F1" s="4" t="inlineStr">
         <is>
-          <t>주의</t>
+          <t>단위</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>입고1(일자/수량)</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>입고2</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>입고3</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>입고 누계(사람 기입)</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
+          <t>잔량</t>
+        </is>
+      </c>
+      <c r="L1" s="4" t="inlineStr">
+        <is>
+          <t>갱신일</t>
+        </is>
+      </c>
+      <c r="M1" s="4" t="inlineStr">
+        <is>
+          <t>갱신자</t>
+        </is>
+      </c>
+      <c r="N1" s="4" t="inlineStr">
+        <is>
+          <t>갱신 상태</t>
+        </is>
+      </c>
+      <c r="O1" s="4" t="inlineStr">
+        <is>
+          <t>확인 필요 사항</t>
+        </is>
+      </c>
+      <c r="P1" s="4" t="inlineStr">
+        <is>
+          <t>사람 확정</t>
+        </is>
+      </c>
+      <c r="Q1" s="4" t="inlineStr">
+        <is>
+          <t>비고(교육용 함정 설명)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>P-01</t>
+          <t>PO-2609-001</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>볼밸브</t>
+          <t>P-03</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>50A</t>
+          <t>PVC 파이프 50A</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>개</t>
+          <t>A현장</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>볼밸브; 볼발브; 밸브; ball valve</t>
+          <t>40</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>P-02(100A)와 별칭이 같음 → 규격 없으면 병합 금지</t>
+          <t>본</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>09-10 / 20</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>09-14 / 20</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr"/>
+      <c r="J2" s="5" t="inlineStr"/>
+      <c r="K2" s="2">
+        <f>IF(J2="","",E2-J2)</f>
+        <v/>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>박지원</t>
+        </is>
+      </c>
+      <c r="N2" s="2">
+        <f>IF(L2="","갱신 누락",IF(M2="","갱신자 없음","기록 있음"))</f>
+        <v/>
+      </c>
+      <c r="O2" s="2" t="inlineStr"/>
+      <c r="P2" s="5" t="inlineStr"/>
+      <c r="Q2" s="2" t="inlineStr">
+        <is>
+          <t>완납</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>P-02</t>
+          <t>PO-2609-002</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>볼밸브</t>
+          <t>P-01</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>100A</t>
+          <t>볼밸브 50A</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
+          <t>A현장</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
           <t>개</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>볼밸브; 볼발브; 밸브; ball valve</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>P-01(50A)와 별칭이 같음 → 규격 없으면 병합 금지</t>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>09-12 / 10</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr"/>
+      <c r="I3" s="2" t="inlineStr"/>
+      <c r="J3" s="5" t="inlineStr"/>
+      <c r="K3" s="2">
+        <f>IF(J3="","",E3-J3)</f>
+        <v/>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>박지원</t>
+        </is>
+      </c>
+      <c r="N3" s="2">
+        <f>IF(L3="","갱신 누락",IF(M3="","갱신자 없음","기록 있음"))</f>
+        <v/>
+      </c>
+      <c r="O3" s="2" t="inlineStr"/>
+      <c r="P3" s="5" t="inlineStr"/>
+      <c r="Q3" s="2" t="inlineStr">
+        <is>
+          <t>잔량 10 — 2차 입고 예정일 미기재</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>P-03</t>
+          <t>PO-2609-003</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>PVC 파이프</t>
+          <t>P-09</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>50A</t>
+          <t>배관 보온재 50A</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>본</t>
+          <t>B현장</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>PVC 파이프; PVC관; PVC파이프; 피브이씨 파이프; pvc pipe</t>
+          <t>120</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>P-04(100A)와 별칭이 같음 → 규격 없으면 병합 금지</t>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>09-11 / 60</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>09-15 / 60</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr"/>
+      <c r="J4" s="5" t="inlineStr"/>
+      <c r="K4" s="2">
+        <f>IF(J4="","",E4-J4)</f>
+        <v/>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>정설비</t>
+        </is>
+      </c>
+      <c r="N4" s="2">
+        <f>IF(L4="","갱신 누락",IF(M4="","갱신자 없음","기록 있음"))</f>
+        <v/>
+      </c>
+      <c r="O4" s="2" t="inlineStr"/>
+      <c r="P4" s="5" t="inlineStr"/>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>2차 입고 후 갱신 안 됨(갱신일이 1차 시점) → 미갱신</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>P-04</t>
+          <t>PO-2609-004</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>PVC 파이프</t>
+          <t>P-10</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>100A</t>
+          <t>테프론 테이프 12mm</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>본</t>
+          <t>C현장</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>PVC 파이프; PVC관; PVC파이프; 피브이씨 파이프; pvc pipe</t>
+          <t>10</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>P-03(50A)와 별칭이 같음 → 규격 없으면 병합 금지</t>
+          <t>롤</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr"/>
+      <c r="H5" s="2" t="inlineStr"/>
+      <c r="I5" s="2" t="inlineStr"/>
+      <c r="J5" s="5" t="inlineStr"/>
+      <c r="K5" s="2">
+        <f>IF(J5="","",E5-J5)</f>
+        <v/>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>한구매</t>
+        </is>
+      </c>
+      <c r="N5" s="2">
+        <f>IF(L5="","갱신 누락",IF(M5="","갱신자 없음","기록 있음"))</f>
+        <v/>
+      </c>
+      <c r="O5" s="2" t="inlineStr"/>
+      <c r="P5" s="5" t="inlineStr"/>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>발주 12일 경과, 입고 기록 없음 → 확인</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
+          <t>PO-2609-005</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
           <t>P-05</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>강관</t>
-        </is>
-      </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>50A</t>
+          <t>강관 50A</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
+          <t>B현장</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>본</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>강관; 백관; 스틸파이프; steel pipe</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>P-06(100A)와 별칭이 같음</t>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>09-13 / 30</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr"/>
+      <c r="I6" s="2" t="inlineStr"/>
+      <c r="J6" s="5" t="inlineStr"/>
+      <c r="K6" s="2">
+        <f>IF(J6="","",E6-J6)</f>
+        <v/>
+      </c>
+      <c r="L6" s="2" t="inlineStr"/>
+      <c r="M6" s="2" t="inlineStr"/>
+      <c r="N6" s="2">
+        <f>IF(L6="","갱신 누락",IF(M6="","갱신자 없음","기록 있음"))</f>
+        <v/>
+      </c>
+      <c r="O6" s="2" t="inlineStr"/>
+      <c r="P6" s="5" t="inlineStr"/>
+      <c r="Q6" s="2" t="inlineStr">
+        <is>
+          <t>입고는 있으나 갱신일·갱신자 공란 → 책임자 확인</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>P-06</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>강관</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>100A</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>본</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>강관; 백관; 스틸파이프; steel pipe</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>P-05(50A)와 별칭이 같음</t>
-        </is>
-      </c>
+      <c r="A7" s="2" t="n"/>
+      <c r="B7" s="2" t="n"/>
+      <c r="C7" s="2" t="n"/>
+      <c r="D7" s="2" t="n"/>
+      <c r="E7" s="2" t="n"/>
+      <c r="F7" s="2" t="n"/>
+      <c r="G7" s="2" t="n"/>
+      <c r="H7" s="2" t="n"/>
+      <c r="I7" s="2" t="n"/>
+      <c r="J7" s="2" t="n"/>
+      <c r="K7" s="2" t="n"/>
+      <c r="L7" s="2" t="n"/>
+      <c r="M7" s="2" t="n"/>
+      <c r="N7" s="2" t="n"/>
+      <c r="O7" s="2" t="n"/>
+      <c r="P7" s="2" t="n"/>
+      <c r="Q7" s="2" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>P-07</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>PVC 엘보 90도</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>50A</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>개</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>엘보; 엘보우; 90도 엘보; elbow</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>P-08(45도)과 '엘보' 별칭 공유 → 각도 확인</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>P-08</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>PVC 엘보 45도</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>50A</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>개</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>엘보; 엘보우; 45도 엘보; 45엘보</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>P-07(90도)과 '엘보' 별칭 공유 → 각도 확인</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>P-09</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>배관 보온재</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>50A</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>보온재; 단열재; 인슐레이션</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>길이 단위(m). 개수로 요청 오면 불일치</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>P-10</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>테프론 테이프</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>12mm</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>롤</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>테프론; 테플론 테이프; 씰테이프; 테프론 테이프</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>롤 단위. 개수로 요청 오면 불일치</t>
-        </is>
-      </c>
+          <t>안내: 입고 누계는 입고 칸을 보고 사람이 적는다(자동 합산하지 않는 이유: 분할 입고 표기가 제각각이라 원문 확인이 먼저). 공동 화면 효과(전화·메신저 확인 감소)를 먼저 기록하고, AI 추가 효과는 분리해 확인한다(기획안 §3-2 게이트).</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n"/>
+      <c r="C8" s="2" t="n"/>
+      <c r="D8" s="2" t="n"/>
+      <c r="E8" s="2" t="n"/>
+      <c r="F8" s="2" t="n"/>
+      <c r="G8" s="2" t="n"/>
+      <c r="H8" s="2" t="n"/>
+      <c r="I8" s="2" t="n"/>
+      <c r="J8" s="2" t="n"/>
+      <c r="K8" s="2" t="n"/>
+      <c r="L8" s="2" t="n"/>
+      <c r="M8" s="2" t="n"/>
+      <c r="N8" s="2" t="n"/>
+      <c r="O8" s="2" t="n"/>
+      <c r="P8" s="2" t="n"/>
+      <c r="Q8" s="2" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
